--- a/powerbi/PowerBI_Data_Model.xlsx
+++ b/powerbi/PowerBI_Data_Model.xlsx
@@ -8,29 +8,29 @@
   </bookViews>
   <sheets>
     <sheet name="_README" sheetId="1" r:id="rId1"/>
-    <sheet name="dim_year" sheetId="2" r:id="rId2"/>
-    <sheet name="dim_scenario" sheetId="3" r:id="rId3"/>
-    <sheet name="dim_program" sheetId="4" r:id="rId4"/>
-    <sheet name="dim_funding_source" sheetId="5" r:id="rId5"/>
-    <sheet name="dim_account" sheetId="6" r:id="rId6"/>
-    <sheet name="dim_provenance" sheetId="7" r:id="rId7"/>
-    <sheet name="dim_benchmark" sheetId="8" r:id="rId8"/>
-    <sheet name="fact_financials" sheetId="9" r:id="rId9"/>
-    <sheet name="fact_program" sheetId="10" r:id="rId10"/>
-    <sheet name="fact_funding" sheetId="11" r:id="rId11"/>
-    <sheet name="fact_budget_variance" sheetId="12" r:id="rId12"/>
-    <sheet name="fact_variance_bridge" sheetId="13" r:id="rId13"/>
-    <sheet name="fact_sensitivity" sheetId="14" r:id="rId14"/>
-    <sheet name="fact_allocation" sheetId="15" r:id="rId15"/>
-    <sheet name="fact_quality_tradeoff" sheetId="16" r:id="rId16"/>
-    <sheet name="fact_provenance" sheetId="17" r:id="rId17"/>
+    <sheet name="01 dim_year" sheetId="2" r:id="rId2"/>
+    <sheet name="02 dim_scenario" sheetId="3" r:id="rId3"/>
+    <sheet name="03 dim_program" sheetId="4" r:id="rId4"/>
+    <sheet name="04 dim_funding_source" sheetId="5" r:id="rId5"/>
+    <sheet name="05 dim_account" sheetId="6" r:id="rId6"/>
+    <sheet name="06 dim_provenance" sheetId="7" r:id="rId7"/>
+    <sheet name="07 dim_benchmark" sheetId="8" r:id="rId8"/>
+    <sheet name="08 fact_financials" sheetId="9" r:id="rId9"/>
+    <sheet name="09 fact_program" sheetId="10" r:id="rId10"/>
+    <sheet name="10 fact_funding" sheetId="11" r:id="rId11"/>
+    <sheet name="11 fact_budget_variance" sheetId="12" r:id="rId12"/>
+    <sheet name="12 fact_variance_bridge" sheetId="13" r:id="rId13"/>
+    <sheet name="13 fact_sensitivity" sheetId="14" r:id="rId14"/>
+    <sheet name="14 fact_allocation" sheetId="15" r:id="rId15"/>
+    <sheet name="15 fact_quality_tradeoff" sheetId="16" r:id="rId16"/>
+    <sheet name="16 fact_provenance" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="229">
   <si>
     <t>Power BI data model</t>
   </si>
@@ -47,7 +47,7 @@
     <t>How to use it</t>
   </si>
   <si>
-    <t>Power BI: Get data &gt; Excel workbook &gt; Import, then tick the sixteen tables listed below. Do not tick this sheet.</t>
+    <t>Power BI: Get data &gt; Excel workbook &gt; Import. In the Navigator tick the sixteen TABLES listed below - not the sheets they sit on, and not this sheet. The table names are what the DAX measures expect.</t>
   </si>
   <si>
     <t>Then</t>
@@ -68,58 +68,109 @@
     <t>Historical figures come from IRS Form 990 filings. Program-level detail and all forward-looking figures are analyst assumptions, not the organization's guidance. See data/SOURCES.md.</t>
   </si>
   <si>
-    <t>Sheet</t>
+    <t>Table to import</t>
   </si>
   <si>
     <t>Rows</t>
   </si>
   <si>
+    <t>Lives on</t>
+  </si>
+  <si>
     <t>dim_year</t>
   </si>
   <si>
+    <t>on sheet 01 dim_year</t>
+  </si>
+  <si>
     <t>dim_scenario</t>
   </si>
   <si>
+    <t>on sheet 02 dim_scenario</t>
+  </si>
+  <si>
     <t>dim_program</t>
   </si>
   <si>
+    <t>on sheet 03 dim_program</t>
+  </si>
+  <si>
     <t>dim_funding_source</t>
   </si>
   <si>
+    <t>on sheet 04 dim_funding_source</t>
+  </si>
+  <si>
     <t>dim_account</t>
   </si>
   <si>
+    <t>on sheet 05 dim_account</t>
+  </si>
+  <si>
     <t>dim_provenance</t>
   </si>
   <si>
+    <t>on sheet 06 dim_provenance</t>
+  </si>
+  <si>
     <t>dim_benchmark</t>
   </si>
   <si>
+    <t>on sheet 07 dim_benchmark</t>
+  </si>
+  <si>
     <t>fact_financials</t>
   </si>
   <si>
+    <t>on sheet 08 fact_financials</t>
+  </si>
+  <si>
     <t>fact_program</t>
   </si>
   <si>
+    <t>on sheet 09 fact_program</t>
+  </si>
+  <si>
     <t>fact_funding</t>
   </si>
   <si>
+    <t>on sheet 10 fact_funding</t>
+  </si>
+  <si>
     <t>fact_budget_variance</t>
   </si>
   <si>
+    <t>on sheet 11 fact_budget_variance</t>
+  </si>
+  <si>
     <t>fact_variance_bridge</t>
   </si>
   <si>
+    <t>on sheet 12 fact_variance_bridge</t>
+  </si>
+  <si>
     <t>fact_sensitivity</t>
   </si>
   <si>
+    <t>on sheet 13 fact_sensitivity</t>
+  </si>
+  <si>
     <t>fact_allocation</t>
   </si>
   <si>
+    <t>on sheet 14 fact_allocation</t>
+  </si>
+  <si>
     <t>fact_quality_tradeoff</t>
   </si>
   <si>
+    <t>on sheet 15 fact_quality_tradeoff</t>
+  </si>
+  <si>
     <t>fact_provenance</t>
+  </si>
+  <si>
+    <t>on sheet 16 fact_provenance</t>
   </si>
   <si>
     <t>FY2019</t>
@@ -1291,24 +1342,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.7109375" customWidth="1"/>
     <col min="2" max="2" width="96.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="26" customHeight="1">
+    <row r="3" spans="1:3" ht="26" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1316,7 +1367,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="26" customHeight="1">
+    <row r="4" spans="1:3" ht="39" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1324,7 +1375,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="26" customHeight="1">
+    <row r="5" spans="1:3" ht="26" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1332,12 +1383,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13" customHeight="1">
+    <row r="7" spans="1:3" ht="13" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -1345,12 +1396,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="26" customHeight="1">
+    <row r="9" spans="1:3" ht="26" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -1358,140 +1409,191 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:2">
+      <c r="C11" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" s="4">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
+      <c r="C12" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B13" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
+      <c r="C13" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B14" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:2">
+      <c r="C14" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B15" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:2">
+      <c r="C15" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B16" s="4">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
+      <c r="C16" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B17" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="C17" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B18" s="4">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
+      <c r="C18" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B19" s="4">
         <v>327</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
+      <c r="C19" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B20" s="4">
         <v>64</v>
       </c>
-    </row>
-    <row r="21" spans="1:2">
+      <c r="C20" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="4" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B21" s="4">
         <v>105</v>
       </c>
-    </row>
-    <row r="22" spans="1:2">
+      <c r="C21" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="B22" s="4">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="1:2">
+      <c r="C22" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B23" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:2">
+      <c r="C23" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="4" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B24" s="4">
         <v>18</v>
       </c>
-    </row>
-    <row r="25" spans="1:2">
+      <c r="C24" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" s="4" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B25" s="4">
         <v>12</v>
       </c>
-    </row>
-    <row r="26" spans="1:2">
+      <c r="C25" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B26" s="4">
         <v>9</v>
       </c>
-    </row>
-    <row r="27" spans="1:2">
+      <c r="C26" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" s="4" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B27" s="4">
         <v>4</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1519,37 +1621,37 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="5" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -3814,22 +3916,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="5" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5774,25 +5876,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="5" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5815,7 +5917,7 @@
         <v>0.12128</v>
       </c>
       <c r="G2" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -5838,7 +5940,7 @@
         <v>-0.042585</v>
       </c>
       <c r="G3" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -5861,7 +5963,7 @@
         <v>1.074572</v>
       </c>
       <c r="G4" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -5884,7 +5986,7 @@
         <v>0.139662</v>
       </c>
       <c r="G5" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -5907,7 +6009,7 @@
         <v>0.064582</v>
       </c>
       <c r="G6" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -5930,7 +6032,7 @@
         <v>0.027616</v>
       </c>
       <c r="G7" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -5953,7 +6055,7 @@
         <v>0.084706</v>
       </c>
       <c r="G8" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -5976,7 +6078,7 @@
         <v>0.06187</v>
       </c>
       <c r="G9" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -5999,7 +6101,7 @@
         <v>0.309848</v>
       </c>
       <c r="G10" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -6022,7 +6124,7 @@
         <v>0.049712</v>
       </c>
       <c r="G11" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -6045,7 +6147,7 @@
         <v>0.08644399999999999</v>
       </c>
       <c r="G12" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -6067,16 +6169,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="5" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -6084,10 +6186,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="D2">
         <v>13476070.13</v>
@@ -6098,10 +6200,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="C3" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="D3">
         <v>658965.11</v>
@@ -6112,10 +6214,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="C4" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="D4">
         <v>211346.87</v>
@@ -6126,10 +6228,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="C5" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="D5">
         <v>14346382.11</v>
@@ -6164,51 +6266,51 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="5" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6252,7 +6354,7 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="B3">
         <v>0.1</v>
@@ -6296,7 +6398,7 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="B4">
         <v>0.2</v>
@@ -6340,7 +6442,7 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="B5">
         <v>0.3</v>
@@ -6384,7 +6486,7 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="B6">
         <v>0.4</v>
@@ -6428,7 +6530,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="B7">
         <v>0.5</v>
@@ -6472,7 +6574,7 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -6516,7 +6618,7 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B9">
         <v>0.1</v>
@@ -6560,7 +6662,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B10">
         <v>0.2</v>
@@ -6604,7 +6706,7 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B11">
         <v>0.3</v>
@@ -6648,7 +6750,7 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B12">
         <v>0.4</v>
@@ -6692,7 +6794,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B13">
         <v>0.5</v>
@@ -6736,7 +6838,7 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -6777,7 +6879,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B15">
         <v>0.1</v>
@@ -6818,7 +6920,7 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B16">
         <v>0.2</v>
@@ -6859,7 +6961,7 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B17">
         <v>0.3</v>
@@ -6900,7 +7002,7 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B18">
         <v>0.4</v>
@@ -6944,7 +7046,7 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B19">
         <v>0.5</v>
@@ -7012,51 +7114,51 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="5" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -7094,10 +7196,10 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="B3" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -7135,10 +7237,10 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -7176,10 +7278,10 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="B5" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -7217,10 +7319,10 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="B6" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -7258,10 +7360,10 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="B7" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -7299,10 +7401,10 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="B8" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -7340,10 +7442,10 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="B9" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -7381,10 +7483,10 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="B10" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -7422,10 +7524,10 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="B11" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -7463,10 +7565,10 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="B12" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -7504,10 +7606,10 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="B13" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -7565,22 +7667,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="5" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7771,18 +7873,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="5" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="B2">
         <v>56</v>
@@ -7793,7 +7895,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="B3">
         <v>19</v>
@@ -7804,7 +7906,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -7815,7 +7917,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="B5">
         <v>135</v>
@@ -7845,19 +7947,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7865,10 +7967,10 @@
         <v>2019</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7882,10 +7984,10 @@
         <v>2020</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -7899,10 +8001,10 @@
         <v>2021</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -7916,10 +8018,10 @@
         <v>2022</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -7933,10 +8035,10 @@
         <v>2023</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -7950,10 +8052,10 @@
         <v>2024</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -7967,10 +8069,10 @@
         <v>2025</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -7984,10 +8086,10 @@
         <v>2026</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -8001,10 +8103,10 @@
         <v>2027</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -8018,10 +8120,10 @@
         <v>2028</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -8035,10 +8137,10 @@
         <v>2029</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -8067,16 +8169,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="5" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -8084,13 +8186,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -8098,13 +8200,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -8112,13 +8214,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8126,13 +8228,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -8159,28 +8261,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8188,13 +8290,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E2">
         <v>61000</v>
@@ -8214,13 +8316,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="E3">
         <v>37000</v>
@@ -8240,13 +8342,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="E4">
         <v>88000</v>
@@ -8266,13 +8368,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="E5">
         <v>46500</v>
@@ -8310,22 +8412,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="5" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8333,10 +8435,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="D2">
         <v>0.12</v>
@@ -8353,10 +8455,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="D3">
         <v>0.21</v>
@@ -8373,10 +8475,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>0.44</v>
@@ -8393,10 +8495,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="D5">
         <v>0.19</v>
@@ -8413,10 +8515,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="D6">
         <v>0.04</v>
@@ -8449,22 +8551,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="5" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8472,13 +8574,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -8492,13 +8594,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -8512,13 +8614,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -8532,13 +8634,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -8552,13 +8654,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -8572,13 +8674,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -8592,13 +8694,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -8612,13 +8714,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -8632,13 +8734,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -8652,13 +8754,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -8672,13 +8774,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -8692,13 +8794,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -8712,13 +8814,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -8732,13 +8834,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -8752,13 +8854,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -8772,13 +8874,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D17" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -8792,13 +8894,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D18" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -8827,16 +8929,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="5" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -8844,10 +8946,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -8858,10 +8960,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -8872,10 +8974,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -8886,10 +8988,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="C5" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -8916,121 +9018,121 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="C2">
         <v>0.65</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="C3">
         <v>0.35</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="E4" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="E5" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B6" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="C6">
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="E6" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="C7">
         <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="E7" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -9054,16 +9156,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="5" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:4">

--- a/powerbi/PowerBI_Data_Model.xlsx
+++ b/powerbi/PowerBI_Data_Model.xlsx
@@ -53,7 +53,7 @@
     <t>Then</t>
   </si>
   <si>
-    <t>Build the relationships and paste the measures from measures.dax. Both steps are in BUILD_GUIDE.md - relationships are NOT carried over by the import and must be created by hand.</t>
+    <t>Build the relationships, then add the measures - measures_dax_query.dax in the browser, measures.dax in Desktop. Both steps are in BUILD_GUIDE.md - relationships are NOT carried over by the import and must be created by hand.</t>
   </si>
   <si>
     <t>Tables in this workbook</t>
@@ -1375,7 +1375,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="26" customHeight="1">
+    <row r="5" spans="1:3" ht="39" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
